--- a/rehearsals/blind-01/out-after-fixes/a1/a1.xlsx
+++ b/rehearsals/blind-01/out-after-fixes/a1/a1.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$Y$210</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$E$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$E$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Date coverage'!$A$1:$E$49</definedName>
@@ -30434,7 +30434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -31448,12 +31448,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-STALE</t>
+          <t>I-AUTO-SUMMARY-ADD-01</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>28 row(s) STALE at ADD-03: a dependency changed after the interpretation was made (dates recomputed; the reading needs a person). Rows: VOL-I-6.3-01, VOL-I-6.4-02, VOL-I-7.1-01, VOL-I-8.3-01, VOL-IV-F4A-01, VOL-I-9.4-01, ADD-02-7.2-01, VOL-I-3.4-01, VOL-I-5.5-01, VOL-I-6.5-02, VOL-I-6.7-01, VOL-I-8.7-01, VOL-I-9.1-01, VOL-I-9.1h-01, VOL-I-9.2-01, VOL-I-9.5-01, VOL-I-9.6-01, VOL-I-9.7-01, VOL-I-10.5-01, VOL-I-10.5-02, VOL-I-10.6-01, VOL-I-12.2-01, VOL-II-5.2-01, VOL-II-6.1-01, VOL-II-7.2-01, VOL-IV-F4A-02, VOL-V-29.3-01, VOL-V-29.4-01</t>
+          <t>ADD-01's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 1 to 6', but ADD-01/Q4 adds an obligation (ADD-01:Q4): 'The geotechnical report in the data room is provided for information. Bidders shall satisfy themselves as to ground conditions.'; [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -31463,24 +31463,20 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>C11 (automatic)</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-6.3-01; VOL-I-6.4-02; VOL-I-7.1-01; VOL-I-8.3-01; VOL-IV-F4A-01; VOL-I-9.4-01; ADD-02-7.2-01; VOL-I-3.4-01; VOL-I-5.5-01; VOL-I-6.5-02; VOL-I-6.7-01; VOL-I-8.7-01; VOL-I-9.1-01; VOL-I-9.1h-01; VOL-I-9.2-01; VOL-I-9.5-01; VOL-I-9.6-01; VOL-I-9.7-01; VOL-I-10.5-01; VOL-I-10.5-02; VOL-I-10.6-01; VOL-I-12.2-01; VOL-II-5.2-01; VOL-II-6.1-01; VOL-II-7.2-01; VOL-IV-F4A-02; VOL-V-29.3-01; VOL-V-29.4-01</t>
-        </is>
-      </c>
+          <t>C28 (automatic)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-COUNTING</t>
+          <t>I-AUTO-SUMMARY-ADD-02</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
+          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -31490,7 +31486,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>D4 (automatic)</t>
+          <t>C28 (automatic)</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -31498,140 +31494,213 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-PENDING-READINGS</t>
+          <t>I-AUTO-SUMMARY-ADD-03</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>20 row(s) rely on image readings (Table 2-4, Form 4-C) still pending the owner's review. Rows: VOL-I-9.4-01, VOL-II-2.5-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-NOTE1, VOL-II-T2-4-OilGrease, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-TSS, VOL-II-T2-4-Turbidity, VOL-II-T2-4-pH, VOL-IV-F4C-01, VOL-IV-F4C-02, VOL-IV-F4C-03, VOL-IV-F4C-04, VOL-IV-F4C-05, VOL-IV-F4C-N1, VOL-V-29.3-01</t>
+          <t>ADD-03's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-03:8.1 states 'A Proposal that quotes an Availability Payment exceeding this amount shall be rejected.'; the summary says only 'inserts a new Volume I Clause 10.5'; [understated] 'responds to clarification requests 15 to 20', but ADD-03/Q16 amends VOL-II:6.1: 'No. In Volume II Clause 6.1, ‘a permanently manned central control room’ is deleted and ‘a central control room manned between 06:00 and 22:00 daily’ is substituted. Volume II Clause 8.3 is unchanged.'; [understated] 'responds to clarification requests 15 to 20', but ADD-03/Q17 adds an obligation (VOL-I:8.5): 'No. Only a reference project for which the consortium member itself was responsible for design, construction or operation will be considered. A reference project of an affiliate will be disregarded.'; [omitted] ADD-03/2.3 amends ADD-01:AppA/proposal-due-date; the summary does not mention it: 'In the revised Form 4-A at Appendix A to Addendum No. 1, the entry against ‘Proposal Due Date’, which was not updated by that Addendum, is corrected to read ‘10 December 2026, 14:00 Riyadh time’.'; [omitted] ADD-03/3.2 amends VOL-I:5.2; the summary does not mention it: 'In Volume I Clause 5.2, ‘Requests received after that time will not be answered.’ is deleted and ‘Requests received after 14:00 Riyadh time on the last day for submission will not be answered.’ is substituted.'; [omitted] ADD-03/8.2 renumbers VOL-I:10.5, VOL-I:10.6; the summary does not mention it: 'Existing Volume I Clauses 10.5 and 10.6 are renumbered 10.6 and 10.7 respectively. A reference to Clause 10.5 or Clause 10.6 in Volumes I to V or in Addenda Nos. 1 and 2, including in the response to clarification request 14 in Addendum No…'; [omitted] ADD-03/9.2 ends the effect of ADD-02:Q13; the summary does not mention it: 'The response to clarification request 13 in Addendum No. 2 is superseded.'; [omitted] ADD-03/11.2 adds an obligation (ADD-03:11.2); the summary does not mention it: 'Bidders shall reflect the amended flow in the hydraulic design submitted under Volume II Section 4.'; [omitted] ADD-03/12.2 adds an obligation (VOL-I:9.4); the summary does not mention it: 'Each member of the Bidder shall give the sixth declaration in its Form 4-C. Volume I Clause 9.4 applies.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>readings (automatic)</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-9.4-01; VOL-II-2.5-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH; VOL-IV-F4C-01; VOL-IV-F4C-02; VOL-IV-F4C-03; VOL-IV-F4C-04; VOL-IV-F4C-05; VOL-IV-F4C-N1; VOL-V-29.3-01</t>
-        </is>
-      </c>
+          <t>C28 (automatic)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>I-A5-attendance-notice</t>
+          <t>I-AUTO-STALE</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>A5 attendance-notice: DEADLINE PASSED (ATTENDANCE-NOTICE = 2026-10-14 is before the status date 2026-11-05; record whether it was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+          <t>28 row(s) STALE at ADD-03: a dependency changed after the interpretation was made (dates recomputed; the reading needs a person). Rows: VOL-I-6.3-01, VOL-I-6.4-02, VOL-I-7.1-01, VOL-I-8.3-01, VOL-IV-F4A-01, VOL-I-9.4-01, ADD-02-7.2-01, VOL-I-3.4-01, VOL-I-5.5-01, VOL-I-6.5-02, VOL-I-6.7-01, VOL-I-8.7-01, VOL-I-9.1-01, VOL-I-9.1h-01, VOL-I-9.2-01, VOL-I-9.5-01, VOL-I-9.6-01, VOL-I-9.7-01, VOL-I-10.5-01, VOL-I-10.5-02, VOL-I-10.6-01, VOL-I-12.2-01, VOL-II-5.2-01, VOL-II-6.1-01, VOL-II-7.2-01, VOL-IV-F4A-02, VOL-V-29.3-01, VOL-V-29.4-01</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
+          <t>C11 (automatic)</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
+          <t>VOL-I-6.3-01; VOL-I-6.4-02; VOL-I-7.1-01; VOL-I-8.3-01; VOL-IV-F4A-01; VOL-I-9.4-01; ADD-02-7.2-01; VOL-I-3.4-01; VOL-I-5.5-01; VOL-I-6.5-02; VOL-I-6.7-01; VOL-I-8.7-01; VOL-I-9.1-01; VOL-I-9.1h-01; VOL-I-9.2-01; VOL-I-9.5-01; VOL-I-9.6-01; VOL-I-9.7-01; VOL-I-10.5-01; VOL-I-10.5-02; VOL-I-10.6-01; VOL-I-12.2-01; VOL-II-5.2-01; VOL-II-6.1-01; VOL-II-7.2-01; VOL-IV-F4A-02; VOL-V-29.3-01; VOL-V-29.4-01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-ratio</t>
+          <t>I-AUTO-COUNTING</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (latest start 2026-10-20 is before the status date 2026-11-05; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
+          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.6-01</t>
-        </is>
-      </c>
+          <t>D4 (automatic)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-certificate</t>
+          <t>I-AUTO-PENDING-READINGS</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-certificate: INFEASIBLE by 7 WD (latest start 2026-10-27 is before the status date 2026-11-05; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
+          <t>20 row(s) rely on image readings (Table 2-4, Form 4-C) still pending the owner's review. Rows: VOL-I-9.4-01, VOL-II-2.5-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-NOTE1, VOL-II-T2-4-OilGrease, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-TSS, VOL-II-T2-4-Turbidity, VOL-II-T2-4-pH, VOL-IV-F4C-01, VOL-IV-F4C-02, VOL-IV-F4C-03, VOL-IV-F4C-04, VOL-IV-F4C-05, VOL-IV-F4C-N1, VOL-V-29.3-01</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
+          <t>readings (automatic)</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-8.6-01</t>
+          <t>VOL-I-9.4-01; VOL-II-2.5-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH; VOL-IV-F4C-01; VOL-IV-F4C-02; VOL-IV-F4C-03; VOL-IV-F4C-04; VOL-IV-F4C-05; VOL-IV-F4C-N1; VOL-V-29.3-01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
+          <t>I-A5-attendance-notice</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>A5 attendance-notice: DEADLINE PASSED (ATTENDANCE-NOTICE = 2026-10-14 is before the status date 2026-11-05; record whether it was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>I-A5-lcc-ratio</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (latest start 2026-10-20 is before the status date 2026-11-05; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.6-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>I-A5-lcc-certificate</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>A5 lcc-certificate: INFEASIBLE by 7 WD (latest start 2026-10-27 is before the status date 2026-11-05; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.6-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
           <t>I-A5-FEASIBILITY</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>A5 at the status date: attendance-notice DEADLINE PASSED; lcc-ratio INFEASIBLE by 12 WD; lcc-certificate INFEASIBLE by 7 WD. Lead times are PROVISIONAL assumptions (A5 drivers)</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Bid manager</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>A5 (automatic)</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>ADD-01-3.1-01; VOL-I-5.4-01; VOL-I-8.6-01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E46"/>
+  <autoFilter ref="A1:E49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/rehearsals/blind-01/out-after-fixes/a1/a1.xlsx
+++ b/rehearsals/blind-01/out-after-fixes/a1/a1.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$J$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Date coverage'!$A$1:$E$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37498,7 +37498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -38378,7 +38378,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>PROVISIONAL ASSUMPTION: courier to the Appendix 3 address before 14:00 on the PDD; not stated</t>
+          <t>PROVISIONAL ASSUMPTION: courier to the Appendix 3 address before the Proposal Due Date time stated in VOL-I 6.1 as amended (the time is derived, not assumed); not stated</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -38830,17 +38830,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>planning.delivery_cutoff_time</t>
+          <t>calendar.holidays</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>configurable planning choice</t>
+          <t>the pack declares none (VOL-I 2.4 excludes declared public holidays)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -38849,30 +38849,8 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>calendar.holidays</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>the pack declares none (VOL-I 2.4 excludes declared public holidays)</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Bid manager</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D62"/>
+  <autoFilter ref="A1:D61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
